--- a/docs/verification/files/rocscience/joints/rj005.xlsx
+++ b/docs/verification/files/rocscience/joints/rj005.xlsx
@@ -15023,7 +15023,7 @@
         </is>
       </c>
       <c r="E3" s="3">
-        <v>0.0</v>
+        <v>132.0790560447</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>

--- a/docs/verification/files/rocscience/joints/rj005.xlsx
+++ b/docs/verification/files/rocscience/joints/rj005.xlsx
@@ -3454,7 +3454,11 @@
       <c r="C23" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="D23" s="1"/>
+      <c r="D23" s="1" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B24" s="1"/>

--- a/docs/verification/files/rocscience/joints/rj005.xlsx
+++ b/docs/verification/files/rocscience/joints/rj005.xlsx
@@ -15015,20 +15015,10 @@
       <c r="A3" s="3">
         <v>1</v>
       </c>
-      <c r="B3" s="3">
-        <v>468.8927935526</v>
-      </c>
-      <c r="C3" s="3">
-        <v>660.0</v>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Depth</t>
-        </is>
-      </c>
-      <c r="E3" s="3">
-        <v>132.0790560447</v>
-      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
@@ -15268,9 +15258,17 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
+      <c r="A3" s="3">
+        <v>560.0</v>
+      </c>
+      <c r="B3" s="3">
+        <v>140.0</v>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
       <c r="E3" t="s">
         <v>221</v>
       </c>
@@ -15279,9 +15277,17 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
+      <c r="A4" s="3">
+        <v>377.7855871052</v>
+      </c>
+      <c r="B4" s="3">
+        <v>400.0</v>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
       <c r="E4" t="s">
         <v>223</v>
       </c>
